--- a/tame_output/ON/bt/strategyON_20240805.xlsx
+++ b/tame_output/ON/bt/strategyON_20240805.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.0%</t>
+          <t>451.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-681.5%</t>
+          <t>-671.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-200.9%</t>
+          <t>-195.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.5%</t>
+          <t>-217.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-64.8%</t>
+          <t>-57.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2045"/>
+  <dimension ref="A1:G2046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725123937759354</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48596,6 +48596,29 @@
       </c>
       <c r="G2045" t="n">
         <v>3.812064705819529</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="2" t="n">
+        <v>45508</v>
+      </c>
+      <c r="B2046" t="n">
+        <v>3.616483965746217</v>
+      </c>
+      <c r="C2046" t="n">
+        <v>3.84597809452615</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>-5.095954691140879</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>1.807239793756052</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>0.06777665148069478</v>
+      </c>
+      <c r="G2046" t="n">
+        <v>3.886644085414567</v>
       </c>
     </row>
   </sheetData>
